--- a/data/excel/v12StagingBODC_Flight.xlsx
+++ b/data/excel/v12StagingBODC_Flight.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE7F1E9-0BB2-4FD3-BD62-9A0C2A04FEAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A0ECE2-D502-4427-9822-79DF1DE39CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flight" sheetId="1" r:id="rId1"/>
@@ -194,7 +194,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3593" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3593" uniqueCount="232">
   <si>
     <t>TestCaseId</t>
   </si>
@@ -862,9 +862,6 @@
     <t>5123456789012346</t>
   </si>
   <si>
-    <t>CFAA@CF91</t>
-  </si>
-  <si>
     <t>SpiceJet</t>
   </si>
   <si>
@@ -875,6 +872,24 @@
   </si>
   <si>
     <t>MarketTypeM</t>
+  </si>
+  <si>
+    <t>k.gaurav</t>
+  </si>
+  <si>
+    <t>07DE6@EAB</t>
+  </si>
+  <si>
+    <t>9-May-2025</t>
+  </si>
+  <si>
+    <t>11-May-2025</t>
+  </si>
+  <si>
+    <t>Universal-69N8</t>
+  </si>
+  <si>
+    <t>Skip Payment</t>
   </si>
 </sst>
 </file>
@@ -1025,7 +1040,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1051,7 +1066,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -13746,7 +13766,7 @@
     <col min="5" max="5" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8.7109375" bestFit="1" customWidth="1"/>
@@ -13878,7 +13898,7 @@
         <v>15</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K1" s="7" t="s">
         <v>17</v>
@@ -13950,7 +13970,7 @@
         <v>52</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AI1" s="2" t="s">
         <v>53</v>
@@ -14192,25 +14212,25 @@
         <v>10</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>174</v>
+        <v>11</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="H2" s="21" t="s">
-        <v>222</v>
+        <v>12</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>227</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>16</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="L2" s="8" t="s">
         <v>25</v>
@@ -14219,16 +14239,16 @@
         <v>187</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="P2" s="9" t="s">
-        <v>200</v>
+        <v>228</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>201</v>
+        <v>229</v>
       </c>
       <c r="R2" s="4" t="s">
         <v>49</v>
@@ -14243,7 +14263,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W2" s="4" t="s">
         <v>46</v>
@@ -14270,19 +14290,19 @@
         <v>1</v>
       </c>
       <c r="AE2" s="4" t="s">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="AF2" s="4" t="s">
         <v>32</v>
       </c>
       <c r="AG2" s="4" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="AH2" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AI2" s="4" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="AJ2" s="8" t="s">
         <v>25</v>
@@ -14297,7 +14317,7 @@
         <v>27</v>
       </c>
       <c r="AN2" s="4" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="AO2" s="9" t="s">
         <v>95</v>
@@ -14363,7 +14383,7 @@
         <v>50</v>
       </c>
       <c r="BJ2" s="4" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="BK2" s="4" t="s">
         <v>101</v>
@@ -14372,7 +14392,7 @@
         <v>0</v>
       </c>
       <c r="BM2" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BN2" s="12" t="s">
         <v>101</v>
@@ -14483,7 +14503,7 @@
         <v>142</v>
       </c>
       <c r="CX2" s="17" t="s">
-        <v>153</v>
+        <v>231</v>
       </c>
       <c r="CY2" s="18" t="s">
         <v>221</v>
@@ -14508,24 +14528,18 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="21">
+  <dataValidations count="22">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CY2" xr:uid="{B56A7B7F-62CE-4138-A926-915460E92EA7}">
       <formula1>"5123456789012346,4111111111111111"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CX2" xr:uid="{85BE43F7-0A3C-4F10-8885-D5F7DB6574C7}">
-      <formula1>"MasterCard,VisaCard"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2" xr:uid="{949CE162-273D-421A-92C7-F3F28FD4579A}">
-      <formula1>"Laxmi@123,Piyush@321,Quad@720,0@7E01E07,CFAA@CF91"</formula1>
+      <formula1>"MasterCard,VisaCard,Skip Payment"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{7C676D75-96AF-48F1-AF31-34B6598565DA}">
       <formula1>"Positive,Negative"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{27CAEE42-B250-4E16-ABF6-E4FF8EA14126}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{FA1D438B-4C7D-40E8-AFEE-7964DDE04682}">
       <formula1>"at,qlabs12345,merg123456"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{F43361C5-91E4-4936-8BF9-59DF52EFACA5}">
-      <formula1>"saurav_at,Piyush,piyush_ql"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2" xr:uid="{4DFACF84-93C1-4C20-A780-9578EDCA3E56}">
       <formula1>"DirectCustomer,Reseller,Corporate"</formula1>
@@ -14572,14 +14586,22 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2 AH2" xr:uid="{C94BBC7D-0C16-417D-872E-1434D4276F15}">
       <formula1>"Domestic,International"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2" xr:uid="{6DE3B66E-1E22-4A24-B8C2-646719D592B6}">
+      <formula1>"EE6B4B@E7,07DE6@EAB,F1CD@9E4B"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2" xr:uid="{6140C80A-87B2-496D-874C-DC3B1FEAF369}">
+      <formula1>"Piyush_ql,ankur_ql,k.gaurav"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2" xr:uid="{AE4733DE-34D3-4630-BE9A-4817FA2D9079}">
+      <formula1>"AeroFloat NDC,Indigo_OTI277,Sabre 5WTF,SABRE NDC,Turkish Airlines NDC,Universal-69N8"</formula1>
+    </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" display="shubham.natkar@quadlabs.com" xr:uid="{EE377F08-6FD5-4E3F-9597-3ADB3AFC752B}"/>
-    <hyperlink ref="H2" r:id="rId2" display="0@7E01E07" xr:uid="{F3BD1CB7-66F7-4053-8E00-E480BD7DDBD2}"/>
-    <hyperlink ref="BT2" r:id="rId3" xr:uid="{9AA167ED-BA5C-434E-A6CC-C421FD8F922F}"/>
-    <hyperlink ref="CC2" r:id="rId4" xr:uid="{6164DD9D-5CE5-46E9-AD39-FCBE19BAFAB7}"/>
+    <hyperlink ref="BT2" r:id="rId1" xr:uid="{9AA167ED-BA5C-434E-A6CC-C421FD8F922F}"/>
+    <hyperlink ref="CC2" r:id="rId2" xr:uid="{6164DD9D-5CE5-46E9-AD39-FCBE19BAFAB7}"/>
+    <hyperlink ref="H2" r:id="rId3" display="EE6B4B@E7" xr:uid="{8A390F2B-42DF-4431-8059-AFA6E34EF20B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId5"/>
+  <legacyDrawing r:id="rId4"/>
 </worksheet>
 </file>